--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(6).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(6).xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\VNovelizerTest_v1.0\Assets\Resources\VNovelizerRes\ExcelVNScripts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="486">
   <si>
     <t>ID</t>
   </si>
@@ -130,9 +135,15 @@
     <t>大卫</t>
   </si>
   <si>
+    <t>David_bandage</t>
+  </si>
+  <si>
     <t>所以，你的意思是，除了履历上的内容外，你小子还在这破地方接受过精神改造？</t>
   </si>
   <si>
+    <t>charfadein(L,1)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_David; 层级=5</t>
   </si>
   <si>
@@ -142,6 +153,9 @@
     <t>他故意摆出了一副轻松幽默的口吻，好像这样就能压制心中的震惊。</t>
   </si>
   <si>
+    <t>charfadeout(L,1)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=6</t>
   </si>
   <si>
@@ -514,7 +528,7 @@
     <t>看着你若有所思但眼神坚定的模样，大卫也不再多问，推开房门便朝着屋外走去。莹白的手电光在走廊的阴翳中划开一条伤口，让你们得以从病房内充斥着消毒剂和秘密的压抑的空气中暂时以喘息。</t>
   </si>
   <si>
-    <t>bgfade(sntzm_david313-315(6)_50,1)</t>
+    <t>bgfade(sntzm_david313-315(6)_50,1)&amp;loadScript(sntzm_david3F(1),1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=47</t>
@@ -664,6 +678,9 @@
     <t>大卫果断地转过身，不再去看你或是你身后疑点重重的病床，莹白的手电光在走廊的阴翳中划开一条伤口，此刻却成为了他用于远离那些阴谋和秘密的逃生通道。</t>
   </si>
   <si>
+    <t>charfadeout(L,1)&amp;bgfade(sntzm_david313-315(6)_50,1)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=31</t>
   </si>
   <si>
@@ -682,6 +699,9 @@
     <t>望着他匆匆离开的背影，你似乎没有别的选择，只能迅速跟上他前进的脚步。在恐惧与猜疑的支配下，为了不让过去的阴影追上自己，你们似乎注定只能如扑火的飞蛾般——以光为引，向暗而生。</t>
   </si>
   <si>
+    <t>loadScript(sntzm_david3F(1),1)</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
@@ -935,6 +955,32 @@
   </si>
   <si>
     <t>留下一个模棱两可的猜想，他转身走出了房间，明亮的手电在走廊里凿出一条闪烁的光带，将他的影子在地上拖得格外的长。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>charfadeout(L,1)&amp;bgfade(sntzm_david313-315(6)_50,1)&amp;loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_david3F(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,1)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=34</t>
@@ -1507,7 +1553,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1517,6 +1563,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1977,31 +2028,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2010,124 +2058,133 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2903,7 +2960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:12">
+    <row r="7" ht="30" spans="1:12">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2914,7 +2971,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -2923,7 +2980,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2935,15 +2992,15 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" ht="27" spans="1:12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" ht="30" spans="1:12">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2952,7 +3009,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -2961,7 +3018,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2973,18 +3030,18 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -2999,7 +3056,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3014,16 +3071,16 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="55.5" spans="1:12">
       <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
@@ -3037,7 +3094,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3052,12 +3109,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3075,7 +3132,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3090,15 +3147,15 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="55.5" spans="1:12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -3113,7 +3170,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3128,12 +3185,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="54" spans="1:12">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3151,7 +3208,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3166,12 +3223,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3204,12 +3261,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="150" spans="1:12">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
@@ -3218,7 +3275,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3227,7 +3284,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3239,15 +3296,15 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" ht="27" spans="1:12">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" ht="30" spans="1:12">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3256,7 +3313,7 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3265,7 +3322,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3280,12 +3337,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="54" spans="1:12">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
@@ -3294,7 +3351,7 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3303,7 +3360,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3318,12 +3375,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="57" spans="1:12">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3332,7 +3389,7 @@
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3341,7 +3398,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3353,18 +3410,18 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3379,7 +3436,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3394,12 +3451,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3417,7 +3474,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3432,15 +3489,15 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" ht="42" spans="1:12">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3455,7 +3512,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3470,12 +3527,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" ht="55.5" spans="1:12">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
@@ -3484,7 +3541,7 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3493,7 +3550,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3505,15 +3562,15 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" ht="55.5" spans="1:12">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3522,7 +3579,7 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3531,7 +3588,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3543,15 +3600,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" ht="55.5" spans="1:12">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3569,7 +3626,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3584,12 +3641,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" ht="42" spans="1:12">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3607,7 +3664,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3622,15 +3679,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3645,7 +3702,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3660,12 +3717,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3683,7 +3740,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3698,15 +3755,15 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3721,7 +3778,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3736,12 +3793,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" ht="57" spans="1:12">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
@@ -3750,7 +3807,7 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3759,7 +3816,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3771,15 +3828,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L29" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" ht="27" spans="1:12">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" ht="30" spans="1:12">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
         <v>32</v>
@@ -3788,7 +3845,7 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3797,7 +3854,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3812,50 +3869,50 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" ht="42" spans="1:12">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" t="s">
         <v>39</v>
       </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" t="s">
-        <v>105</v>
-      </c>
-      <c r="H31" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" t="s">
-        <v>15</v>
-      </c>
-      <c r="K31" t="s">
-        <v>15</v>
-      </c>
       <c r="L31" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" ht="40.5" spans="1:12">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3873,7 +3930,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3888,12 +3945,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" ht="57" spans="1:12">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
@@ -3902,7 +3959,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3911,7 +3968,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3923,53 +3980,53 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" ht="27" spans="1:12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" ht="30" spans="1:12">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" t="s">
         <v>39</v>
       </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" t="s">
-        <v>114</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
-      </c>
-      <c r="K34" t="s">
-        <v>15</v>
-      </c>
       <c r="L34" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" ht="54" spans="1:12">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3987,7 +4044,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4002,15 +4059,15 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" ht="27" spans="1:12">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -4025,7 +4082,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4040,12 +4097,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
         <v>32</v>
@@ -4054,7 +4111,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4063,7 +4120,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4075,15 +4132,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L37" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4092,7 +4149,7 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4101,7 +4158,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4116,12 +4173,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" ht="57" spans="1:12">
       <c r="A39" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
         <v>32</v>
@@ -4130,7 +4187,7 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4139,7 +4196,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4154,12 +4211,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4168,7 +4225,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4177,7 +4234,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4189,18 +4246,18 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L40" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4215,7 +4272,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4230,15 +4287,15 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -4253,7 +4310,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4268,12 +4325,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" ht="67.5" spans="1:12">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4291,7 +4348,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4306,12 +4363,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" ht="67.5" spans="1:12">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4329,7 +4386,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4341,15 +4398,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L44" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45" ht="30" spans="1:12">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s">
         <v>32</v>
@@ -4358,7 +4415,7 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4367,7 +4424,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4379,15 +4436,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L45" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4396,7 +4453,7 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4405,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4417,15 +4474,15 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L46" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4443,7 +4500,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4458,15 +4515,15 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" ht="27" spans="1:12">
       <c r="A48" t="s">
-        <v>156</v>
-      </c>
-      <c r="B48" t="s">
-        <v>13</v>
+        <v>159</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -4481,7 +4538,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4496,12 +4553,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" ht="54" spans="1:12">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4519,27 +4576,25 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
       </c>
-      <c r="I49" t="s">
-        <v>15</v>
-      </c>
+      <c r="I49"/>
       <c r="J49" t="s">
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L49" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
         <v>32</v>
@@ -4548,7 +4603,7 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4557,7 +4612,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4569,15 +4624,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L50" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" ht="54" spans="1:12">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4586,7 +4641,7 @@
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4595,7 +4650,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4607,15 +4662,15 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L51" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" ht="55.5" spans="1:12">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s">
         <v>32</v>
@@ -4624,7 +4679,7 @@
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4633,7 +4688,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4645,15 +4700,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L52" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" ht="55.5" spans="1:12">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B53" t="s">
         <v>32</v>
@@ -4662,7 +4717,7 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4671,7 +4726,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4686,12 +4741,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B54" t="s">
         <v>32</v>
@@ -4700,7 +4755,7 @@
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4709,7 +4764,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4724,12 +4779,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4738,7 +4793,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4747,7 +4802,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4762,12 +4817,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" ht="27" spans="1:12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
         <v>32</v>
@@ -4776,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4785,7 +4840,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4800,12 +4855,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B57" t="s">
         <v>32</v>
@@ -4814,7 +4869,7 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4823,7 +4878,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4838,12 +4893,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4852,7 +4907,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4861,7 +4916,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4873,15 +4928,15 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L58" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" ht="40.5" spans="1:12">
       <c r="A59" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4899,7 +4954,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4914,12 +4969,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4937,7 +4992,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4952,12 +5007,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" ht="67.5" spans="1:12">
       <c r="A61" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B61" t="s">
         <v>32</v>
@@ -4966,7 +5021,7 @@
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -4975,7 +5030,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4987,15 +5042,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L61" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" ht="42" spans="1:12">
       <c r="A62" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5004,7 +5059,7 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5013,7 +5068,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5025,15 +5080,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L62" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" ht="43.5" spans="1:12">
       <c r="A63" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5051,7 +5106,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5066,12 +5121,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64" ht="72" spans="1:12">
       <c r="A64" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5089,7 +5144,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5104,12 +5159,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="65" ht="42" spans="1:12">
       <c r="A65" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5127,7 +5182,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5142,12 +5197,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5165,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5180,12 +5235,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B67" t="s">
         <v>32</v>
@@ -5194,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -5203,7 +5258,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5215,15 +5270,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L67" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" ht="54" spans="1:12">
       <c r="A68" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5232,7 +5287,7 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5241,7 +5296,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5253,15 +5308,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="L68" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69" ht="67.5" spans="1:12">
       <c r="A69" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5279,7 +5334,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5294,12 +5349,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" ht="55.5" spans="1:12">
       <c r="A70" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5317,27 +5372,25 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
       </c>
-      <c r="I70" t="s">
-        <v>15</v>
-      </c>
+      <c r="I70"/>
       <c r="J70" t="s">
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L70" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5375,7 +5428,7 @@
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5393,7 +5446,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5408,12 +5461,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" ht="27" spans="1:12">
       <c r="A73" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5431,7 +5484,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5451,7 +5504,7 @@
     </row>
     <row r="74" ht="42" spans="1:12">
       <c r="A74" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5469,7 +5522,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5484,12 +5537,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="75" ht="54" spans="1:12">
       <c r="A75" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5507,7 +5560,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5522,15 +5575,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" ht="42" spans="1:12">
       <c r="A76" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5545,7 +5598,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5560,12 +5613,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5583,7 +5636,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5598,15 +5651,15 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" ht="69" spans="1:12">
       <c r="A78" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B78" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5621,7 +5674,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5636,12 +5689,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5659,7 +5712,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5674,12 +5727,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="80" ht="57" spans="1:12">
       <c r="A80" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B80" t="s">
         <v>32</v>
@@ -5688,7 +5741,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -5697,7 +5750,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5709,15 +5762,15 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L80" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B81" t="s">
         <v>32</v>
@@ -5726,7 +5779,7 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E81" t="s">
         <v>15</v>
@@ -5735,7 +5788,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5750,12 +5803,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" ht="54" spans="1:12">
       <c r="A82" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5764,7 +5817,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -5773,7 +5826,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5785,18 +5838,18 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L82" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -5811,7 +5864,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5826,12 +5879,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84" ht="30" spans="1:12">
       <c r="A84" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B84" t="s">
         <v>32</v>
@@ -5840,7 +5893,7 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -5849,7 +5902,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5861,15 +5914,15 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L84" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" ht="40.5" spans="1:12">
       <c r="A85" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -5878,7 +5931,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -5887,7 +5940,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5899,15 +5952,15 @@
         <v>15</v>
       </c>
       <c r="K85" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L85" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B86" t="s">
         <v>32</v>
@@ -5916,7 +5969,7 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
@@ -5925,7 +5978,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -5940,12 +5993,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="87" ht="27" spans="1:12">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" ht="30" spans="1:12">
       <c r="A87" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -5954,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -5963,7 +6016,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -5978,12 +6031,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="88" ht="27" spans="1:12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B88" t="s">
         <v>32</v>
@@ -5992,7 +6045,7 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6001,7 +6054,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6016,12 +6069,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" ht="55.5" spans="1:12">
       <c r="A89" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6030,7 +6083,7 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -6039,7 +6092,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6051,18 +6104,18 @@
         <v>15</v>
       </c>
       <c r="K89" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L89" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" ht="28.5" spans="1:12">
       <c r="A90" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -6077,7 +6130,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6092,15 +6145,15 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" ht="55.5" spans="1:12">
       <c r="A91" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B91" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -6115,7 +6168,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6130,12 +6183,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B92" t="s">
         <v>32</v>
@@ -6144,7 +6197,7 @@
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -6153,7 +6206,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6165,15 +6218,15 @@
         <v>15</v>
       </c>
       <c r="K92" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L92" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" ht="40.5" spans="1:12">
       <c r="A93" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6182,7 +6235,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -6191,7 +6244,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6203,18 +6256,18 @@
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L93" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="94" ht="27" spans="1:12">
       <c r="A94" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -6229,7 +6282,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6244,12 +6297,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6267,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6282,15 +6335,15 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" ht="54" spans="1:12">
       <c r="A96" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -6305,7 +6358,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6320,15 +6373,15 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="97" ht="54" spans="1:12">
       <c r="A97" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B97" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -6343,7 +6396,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6358,12 +6411,12 @@
         <v>18</v>
       </c>
       <c r="L97" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6381,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6396,12 +6449,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="99" ht="30" spans="1:12">
       <c r="A99" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B99" t="s">
         <v>32</v>
@@ -6410,7 +6463,7 @@
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E99" t="s">
         <v>15</v>
@@ -6419,7 +6472,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6431,15 +6484,15 @@
         <v>15</v>
       </c>
       <c r="K99" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L99" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" ht="40.5" spans="1:12">
       <c r="A100" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6448,7 +6501,7 @@
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E100" t="s">
         <v>15</v>
@@ -6457,7 +6510,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6472,12 +6525,12 @@
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="101" ht="40.5" spans="1:12">
       <c r="A101" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B101" t="s">
         <v>32</v>
@@ -6486,7 +6539,7 @@
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E101" t="s">
         <v>15</v>
@@ -6495,7 +6548,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6510,12 +6563,12 @@
         <v>15</v>
       </c>
       <c r="L101" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102" ht="40.5" spans="1:12">
       <c r="A102" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B102" t="s">
         <v>32</v>
@@ -6524,7 +6577,7 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
@@ -6533,7 +6586,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6544,16 +6597,13 @@
       <c r="J102" t="s">
         <v>15</v>
       </c>
-      <c r="K102" t="s">
-        <v>15</v>
-      </c>
       <c r="L102" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="103" ht="40.5" spans="1:12">
       <c r="A103" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
@@ -6562,7 +6612,7 @@
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E103" t="s">
         <v>15</v>
@@ -6571,22 +6621,20 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
       </c>
-      <c r="I103" t="s">
-        <v>15</v>
-      </c>
+      <c r="I103"/>
       <c r="J103" t="s">
         <v>15</v>
       </c>
-      <c r="K103" t="s">
-        <v>15</v>
+      <c r="K103" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="L103" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -6607,39 +6655,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6647,82 +6695,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B12" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B14" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -6744,616 +6792,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D4" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E4" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F4" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E5" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="F5" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D6" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E6" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F6" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D7" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E7" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F7" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B8" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C8" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E8" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F8" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C9" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E9" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F9" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B10" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D10" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E10" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F10" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B11" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C11" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D11" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E11" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F11" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C12" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D12" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E12" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="F12" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B13" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C13" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D13" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E13" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F13" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B14" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C14" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E14" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F14" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B15" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C15" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D15" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E15" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F15" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B16" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C16" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D16" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E16" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F16" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B17" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C17" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D17" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E17" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F17" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C18" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D18" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E18" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="F18" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B19" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C19" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D19" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E19" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B20" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C20" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D20" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E20" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="F20" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B21" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D21" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E21" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F21" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B22" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D22" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E22" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F22" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B23" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C23" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D23" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E23" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F23" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B24" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C24" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D24" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E24" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F24" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B25" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C25" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D25" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E25" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F25" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B26" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C26" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D26" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E26" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F26" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B27" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C27" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D27" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E27" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F27" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B28" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C28" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D28" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E28" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="F28" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B29" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C29" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D29" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E29" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F29" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B30" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C30" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D30" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E30" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F30" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B31" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C31" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D31" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
